--- a/web/public/templates/users_template.xlsx
+++ b/web/public/templates/users_template.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -454,7 +454,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,11 +483,6 @@
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>password</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>vendor_uid</t>
         </is>
@@ -511,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -624,7 +618,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>vendor_uid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,23 +627,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Initial password (defaults to password123 if blank).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>vendor_uid</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>Required for employee/vendor roles. Must exist, e.g. VND-001.</t>
         </is>
